--- a/Assets/Document/云熹约定项目文档/11.配音文本/陈予荣配音文本.xlsx
+++ b/Assets/Document/云熹约定项目文档/11.配音文本/陈予荣配音文本.xlsx
@@ -29,10 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>角色分析：工程师，气质更偏向理性、冷静、书卷气。说话语速不疾不徐，几乎没有情感起伏，喜欢用材料学、热力学、结构力学等理科思维解构日常事物。习惯用数据和逻辑说话，坦荡真诚，不擅长（或不屑于）社交辞令。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>328字</t>
   </si>
@@ -43,16 +40,16 @@
     <t>语气</t>
   </si>
   <si>
-    <t>“左边那款的溢价严重，纯属消费主义构建的智商税。建议你拿右边那个。”</t>
+    <t>“左边那款的溢价严重，纯属消费主义构建的智商税，建议你拿右边那个。”</t>
   </si>
   <si>
     <t>清冷、平缓，像是在陈述一个客观事实，不带任何搭讪或讨好的意味。语气笃定、直接，甚至有几分“学术指导”的冷淡感。</t>
   </si>
   <si>
-    <t>“这只是文字游戏。从材料学的角度来看，左边那款为了追求所谓的古法，面粉的吸水率和酵母的发酵力分布并不均匀。你可以注意看它表面的气孔结构，边缘区域出现了明显的坍塌塌陷。”</t>
-  </si>
-  <si>
-    <t>语速不疾不徐，目光像在审视工业图纸。语气冷静、理性，带着学术报告的精确感。“你可以注意看”说得很平，不是建议，而是指引。</t>
+    <t>“这只是文字游戏，从材料学的角度来看，左边那款为了追求所谓的古法，面粉的吸水率和酵母的发酵力分布并不均匀。你可以注意看它表面的气孔结构，边缘区域出现了明显的坍塌塌陷。”</t>
+  </si>
+  <si>
+    <t>语速不疾不徐，语气冷静、理性，带着学术报告的精确感。“你可以注意看”说得很平，不是建议，而是指引。</t>
   </si>
   <si>
     <t>“相比之下，这款采用了标准化的温控烘焙，它的美拉德反应温度被精确控制在了合理阈值，其内部的面筋网络结构更加稳定。”</t>
@@ -67,7 +64,7 @@
     <t>语气冷静，但“绝对的数据碾压”几个字可以带出极轻微的一丝笃定的自信。</t>
   </si>
   <si>
-    <t>“你说的没错，我的推断只停留在理论模型上，缺乏实际的数据支撑。这是我逻辑上的疏漏。”</t>
+    <t>“你说的没错，我的推断只停留在理论模型上，缺乏实际的数据支撑，这是我逻辑上的疏漏。”</t>
   </si>
   <si>
     <t>语气坦荡、认真，带着学术研讨中的自省和诚恳。没有尴尬或窘迫。</t>
@@ -76,7 +73,7 @@
     <t>“所以我希望能和你一起验证，这两款吐司在风味上是否真的存在差距。”</t>
   </si>
   <si>
-    <t>语气平稳，但多了一丝诚恳的邀请。不是暧昧或讨好，而是像邀请同行共同完成一个实验。</t>
+    <t>语气平稳，但多了一丝诚恳的邀请，不是暧昧或讨好</t>
   </si>
   <si>
     <t>“你大可以放心收下，就当是我为获得新视角支付的受教成本。”</t>
@@ -107,19 +104,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -288,18 +279,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -659,52 +644,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
@@ -719,96 +707,90 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1133,97 +1115,96 @@
     <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="102" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="25.5" spans="1:2">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+    </row>
+    <row r="2" ht="14.25"/>
+    <row r="3" ht="26.25" spans="1:2">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="26.25" spans="1:2">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" ht="37.5" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" ht="37.5" spans="1:2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" ht="37.5" spans="1:2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" ht="18.75" spans="1:2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" ht="18.75" spans="1:2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" ht="18.75" spans="1:2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" ht="18.75" spans="1:2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" ht="18.75" spans="1:2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" ht="19.5" spans="1:2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
